--- a/data/Negociado_de_Policia/npprDesp.xlsx
+++ b/data/Negociado_de_Policia/npprDesp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Negociado_de_Policia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E7D32F-F749-4402-A5C0-37D9DF81737F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F36B96C-C7C4-45BA-9D4B-EF368A5A1CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2496" yWindow="2988" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -78,6 +78,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -87,7 +93,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -95,16 +101,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -330,7 +354,7 @@
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -365,7 +389,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -396,11 +420,11 @@
       <c r="J2" s="3">
         <v>152</v>
       </c>
-      <c r="K2">
-        <v>109</v>
+      <c r="K2" s="4">
+        <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -431,11 +455,11 @@
       <c r="J3" s="3">
         <v>142</v>
       </c>
-      <c r="K3">
-        <v>104</v>
+      <c r="K3" s="4">
+        <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -466,11 +490,11 @@
       <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -501,11 +525,11 @@
       <c r="J5" s="3">
         <v>110</v>
       </c>
-      <c r="K5">
-        <v>57</v>
+      <c r="K5" s="4">
+        <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -536,11 +560,11 @@
       <c r="J6" s="3">
         <v>106</v>
       </c>
-      <c r="K6">
-        <v>51</v>
+      <c r="K6" s="4">
+        <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -571,11 +595,12 @@
       <c r="J7" s="3">
         <v>4</v>
       </c>
-      <c r="K7">
-        <v>6</v>
+      <c r="K7" s="4">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Negociado_de_Policia/npprDesp.xlsx
+++ b/data/Negociado_de_Policia/npprDesp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Negociado_de_Policia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F36B96C-C7C4-45BA-9D4B-EF368A5A1CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305545F0-3A56-4419-85FA-055766DBCDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2496" yWindow="2988" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2964" yWindow="1848" windowWidth="12072" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -421,7 +421,7 @@
         <v>152</v>
       </c>
       <c r="K2" s="4">
-        <v>126</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -456,7 +456,7 @@
         <v>142</v>
       </c>
       <c r="K3" s="4">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -491,7 +491,7 @@
         <v>10</v>
       </c>
       <c r="K4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -526,7 +526,7 @@
         <v>110</v>
       </c>
       <c r="K5" s="4">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -561,7 +561,7 @@
         <v>106</v>
       </c>
       <c r="K6" s="4">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -596,7 +596,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
